--- a/data/employees/EMP072/AST-EMP072-06.xlsx
+++ b/data/employees/EMP072/AST-EMP072-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Resource Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,210 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Project Resource Tracker - Jordan Nguyen (Engineering)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Jordan Nguyen | Role: Engineer | Location: Hsinchu | Date: 2025-03-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp072 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>77</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp072 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>72</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Milestone</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Resources</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp072 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>97</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Proj Alpha</t>
+          <t>EMP072</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M1 - Design</t>
+          <t>Ast Emp072 06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Team A</t>
+          <t>2026-W04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2025-01-29</t>
-        </is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>82</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>4</v>
+          <t>Section 1: Fabric semantic model planning. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Proj Beta</t>
+          <t>EMP072</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M2 - Build</t>
+          <t>Ast Emp072 06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Team B</t>
+          <t>2026-W05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2025-03-20</t>
-        </is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>69</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Delayed</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>6</v>
+          <t>Section 1: Operational risk review. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Proj Gamma</t>
+          <t>EMP072</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M1 - Design</t>
+          <t>Ast Emp072 06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Team C</t>
+          <t>2026-W06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2025-04-01</t>
-        </is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>77</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>On Track</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>3</v>
+          <t>Section 1: Knowledge transfer and onboarding. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Proj Delta</t>
+          <t>EMP072</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M3 - Test</t>
+          <t>Ast Emp072 06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Team A</t>
+          <t>2026-W07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
-        </is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>77</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>At Risk</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>5</v>
+          <t>Section 1: Operational risk review. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp072 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>95</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp072 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>74</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp072 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>80</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp072 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>89</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp072 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>74</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp072 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>63</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp072 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>67</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp072 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>61</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp072 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>85</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp072 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>92</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp072 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>79</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp072 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>67</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp072 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>71</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp072 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>73</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp072 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>61</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp072 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>79</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp072 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>74</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP072</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP072 contributes to ast emp072 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>